--- a/data/Finger_Pressure_Acupuncture_and_Moxacauterization/data.xlsx
+++ b/data/Finger_Pressure_Acupuncture_and_Moxacauterization/data.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M348"/>
+  <dimension ref="A1:M349"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5734,25 +5734,25 @@
         <v>130</v>
       </c>
       <c r="B131" t="str">
-        <v>高松普門堂鍼灸院</v>
+        <v>UETA鍼灸</v>
       </c>
       <c r="C131" t="str">
-        <v>佐々木　文夫</v>
+        <v>植田　浩章</v>
       </c>
       <c r="D131" t="str">
-        <v>34.335024</v>
+        <v>34.32800</v>
       </c>
       <c r="E131" t="str">
-        <v>134.087658</v>
+        <v>134.06640</v>
       </c>
       <c r="F131" t="str">
-        <v>香川県高松市春日町１５９３番地１　春日町事務所１Ａ−１０２</v>
+        <v>高松市上福岡町８９２－３　エミナール上福岡１F</v>
       </c>
       <c r="G131" t="str">
-        <v>087-899-6861</v>
+        <v/>
       </c>
       <c r="H131" t="str">
-        <v>2017/04/01</v>
+        <v>2026/02/05</v>
       </c>
       <c r="I131" t="str">
         <v/>
@@ -14602,7 +14602,7 @@
         <v>134.06110</v>
       </c>
       <c r="F347" t="str">
-        <v>高松市多賀町二丁目１２－８　Ｔハイツ１０１</v>
+        <v>高松市多賀町二丁目１２−８　Ｔハイツ１０１</v>
       </c>
       <c r="G347" t="str">
         <v>087-800-7065</v>
@@ -14667,9 +14667,41 @@
         <v/>
       </c>
     </row>
+    <row r="349">
+      <c r="A349" t="str">
+        <v>351</v>
+      </c>
+      <c r="B349" t="str">
+        <v>いまじん鍼灸院</v>
+      </c>
+      <c r="C349" t="str">
+        <v>辻󠄀　泰司</v>
+      </c>
+      <c r="D349" t="str">
+        <v>34.34392</v>
+      </c>
+      <c r="E349" t="str">
+        <v>134.05159</v>
+      </c>
+      <c r="F349" t="str">
+        <v>高松市今新町８－１６</v>
+      </c>
+      <c r="H349" t="str">
+        <v>2026/02/14</v>
+      </c>
+      <c r="J349" t="str">
+        <v>○</v>
+      </c>
+      <c r="K349" t="str">
+        <v>○</v>
+      </c>
+      <c r="M349" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M348"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M349"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/Finger_Pressure_Acupuncture_and_Moxacauterization/data.xlsx
+++ b/data/Finger_Pressure_Acupuncture_and_Moxacauterization/data.xlsx
@@ -5746,7 +5746,7 @@
         <v>134.06640</v>
       </c>
       <c r="F131" t="str">
-        <v>高松市上福岡町８９２－３　エミナール上福岡１F</v>
+        <v>高松市上福岡町８９２−３　エミナール上福岡１F</v>
       </c>
       <c r="G131" t="str">
         <v/>
@@ -6393,7 +6393,7 @@
         <v>明気通鍼灸院（アキツ）</v>
       </c>
       <c r="C147" t="str">
-        <v>末沢　彰一</v>
+        <v>末澤　彰一</v>
       </c>
       <c r="D147" t="str">
         <v>34.293781</v>
@@ -14684,16 +14684,25 @@
         <v>134.05159</v>
       </c>
       <c r="F349" t="str">
-        <v>高松市今新町８－１６</v>
+        <v>高松市今新町８−１６</v>
+      </c>
+      <c r="G349" t="str">
+        <v/>
       </c>
       <c r="H349" t="str">
         <v>2026/02/14</v>
       </c>
+      <c r="I349" t="str">
+        <v/>
+      </c>
       <c r="J349" t="str">
         <v>○</v>
       </c>
       <c r="K349" t="str">
         <v>○</v>
+      </c>
+      <c r="L349" t="str">
+        <v/>
       </c>
       <c r="M349" t="str">
         <v/>

--- a/data/Finger_Pressure_Acupuncture_and_Moxacauterization/data.xlsx
+++ b/data/Finger_Pressure_Acupuncture_and_Moxacauterization/data.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M349"/>
+  <dimension ref="A1:M352"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2413,34 +2413,34 @@
         <v>49</v>
       </c>
       <c r="B50" t="str">
-        <v>スーパー銭湯あかね温泉治療院</v>
+        <v>こころ鍼灸院</v>
       </c>
       <c r="C50" t="str">
-        <v>遠藤　正男</v>
+        <v>新家　佳代</v>
       </c>
       <c r="D50" t="str">
-        <v>34.350780</v>
+        <v>34.33954</v>
       </c>
       <c r="E50" t="str">
-        <v>134.023628</v>
+        <v>134.11325</v>
       </c>
       <c r="F50" t="str">
-        <v>香川県高松市茜町２８番４３号</v>
+        <v>高松市高松町２４２０－１１</v>
       </c>
       <c r="G50" t="str">
-        <v>087-833-0268</v>
+        <v>090-7148-1659</v>
       </c>
       <c r="H50" t="str">
-        <v>2000/06/01</v>
+        <v>2023/03/15</v>
       </c>
       <c r="I50" t="str">
-        <v>○</v>
+        <v/>
       </c>
       <c r="J50" t="str">
-        <v/>
+        <v>○</v>
       </c>
       <c r="K50" t="str">
-        <v/>
+        <v>○</v>
       </c>
       <c r="L50" t="str">
         <v/>
@@ -11556,25 +11556,25 @@
         <v>274</v>
       </c>
       <c r="B273" t="str">
-        <v>なお治療院</v>
+        <v>なお鍼灸指圧治療院</v>
       </c>
       <c r="C273" t="str">
         <v>間島　直行</v>
       </c>
       <c r="D273" t="str">
-        <v>34.338454</v>
+        <v>34.34654</v>
       </c>
       <c r="E273" t="str">
-        <v>134.055717</v>
+        <v>134.03787</v>
       </c>
       <c r="F273" t="str">
-        <v>香川県高松市塩上町二丁目１２番９号</v>
+        <v>高松市扇町１－２３－２３</v>
       </c>
       <c r="G273" t="str">
-        <v>087-861-7088</v>
+        <v/>
       </c>
       <c r="H273" t="str">
-        <v>2018/10/02</v>
+        <v>2026/03/13</v>
       </c>
       <c r="I273" t="str">
         <v>○</v>
@@ -14708,9 +14708,90 @@
         <v/>
       </c>
     </row>
+    <row r="350">
+      <c r="A350" t="str">
+        <v>352</v>
+      </c>
+      <c r="B350" t="str">
+        <v>今橋鍼灸治療院</v>
+      </c>
+      <c r="C350" t="str">
+        <v>井上　敏男</v>
+      </c>
+      <c r="D350" t="str">
+        <v>34.34262</v>
+      </c>
+      <c r="E350" t="str">
+        <v>134.05946</v>
+      </c>
+      <c r="F350" t="str">
+        <v>高松市松福町１－１８－１８</v>
+      </c>
+      <c r="H350" t="str">
+        <v>2026/04/01</v>
+      </c>
+      <c r="I350" t="str">
+        <v>○</v>
+      </c>
+      <c r="J350" t="str">
+        <v>○</v>
+      </c>
+      <c r="K350" t="str">
+        <v>○</v>
+      </c>
+      <c r="M350" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="str">
+        <v>353</v>
+      </c>
+      <c r="B351" t="str">
+        <v>角陸鍼灸マッサージ治療院</v>
+      </c>
+      <c r="C351" t="str">
+        <v>角陸　功一</v>
+      </c>
+      <c r="D351" t="str">
+        <v>34.34571</v>
+      </c>
+      <c r="E351" t="str">
+        <v>134.03667</v>
+      </c>
+      <c r="F351" t="str">
+        <v>高松市扇町一丁目２５－１６</v>
+      </c>
+      <c r="H351" t="str">
+        <v>2026/04/01</v>
+      </c>
+      <c r="I351" t="str">
+        <v>○</v>
+      </c>
+      <c r="J351" t="str">
+        <v>○</v>
+      </c>
+      <c r="K351" t="str">
+        <v>○</v>
+      </c>
+      <c r="M351" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="352">
+      <c r="D352" t="str">
+        <v/>
+      </c>
+      <c r="E352" t="str">
+        <v/>
+      </c>
+      <c r="M352" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M349"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M352"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/Finger_Pressure_Acupuncture_and_Moxacauterization/data.xlsx
+++ b/data/Finger_Pressure_Acupuncture_and_Moxacauterization/data.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L352"/>
+  <dimension ref="A1:L353"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -13754,7 +13754,7 @@
         <v>134.06666</v>
       </c>
       <c r="F352" t="str">
-        <v>高松市林町２５６３－１６</v>
+        <v>高松市林町２５６３−１６</v>
       </c>
       <c r="G352" t="str">
         <v>2026/04/08</v>
@@ -13775,9 +13775,38 @@
         <v/>
       </c>
     </row>
+    <row r="353">
+      <c r="A353" t="str">
+        <v>357</v>
+      </c>
+      <c r="B353" t="str">
+        <v>ＨＡＲＩ．ＳＴＡ高松はり院</v>
+      </c>
+      <c r="C353" t="str">
+        <v>江並　良真</v>
+      </c>
+      <c r="D353" t="str">
+        <v>34.32593</v>
+      </c>
+      <c r="E353" t="str">
+        <v>134.07938</v>
+      </c>
+      <c r="F353" t="str">
+        <v>高松市木太町３５９１－２ＭｕｒａｋａｍｉＢｕｉｌ２階北</v>
+      </c>
+      <c r="G353" t="str">
+        <v>2026/05/06</v>
+      </c>
+      <c r="I353" t="str">
+        <v>○</v>
+      </c>
+      <c r="L353" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L352"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L353"/>
   </ignoredErrors>
 </worksheet>
 </file>